--- a/assets/constructions/examples/ctd_mib_rou.xlsx
+++ b/assets/constructions/examples/ctd_mib_rou.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT200-080A27R08RD16</t>
+          <t>MT200-042A16R05RD10-IK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -593,40 +613,40 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>61.4</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>4500</v>
+        <v>18500</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RDN..1605MO..N</t>
+          <t>RDN..10T3MO..N</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -634,12 +654,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
+          <t>ISO_6462:FDAxx016</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>SKIF_RD10T3H</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -649,17 +669,17 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>SKIF_RD10T3H</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -669,56 +689,64 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JRC-6R50-25.4-4T</t>
+          <t>R200-064Q27-16M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JCR</t>
+          <t>CoroMillⓇ 200 face milling cutter</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>25.4</v>
+        <v>27</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>13100</v>
+      </c>
       <c r="M3" t="n">
-        <v>0.35</v>
+        <v>0.856</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RC*T1204</t>
+          <t>metric RCKT 1606M0</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -726,12 +754,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx025.4</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>DER_RC1204H</t>
+          <t>COR_RC1606H</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -751,119 +779,123 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RC1204_H</t>
+          <t>SAND_RC1606_H</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M200D50Z04RN16</t>
+          <t>MT200-100B32R09RD16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M200</t>
-        </is>
-      </c>
+          <t>СКИФ-М</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G4" t="n">
-        <v>42</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.49</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>26700</v>
+        <v>4000</v>
       </c>
       <c r="M4" t="n">
-        <v>0.36</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>RDN..1605MO..N</t>
+        </is>
+      </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx032</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>WIDIA_RN1605H</t>
+          <t>SKIF_RD1605H</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>WID_RN1605_H</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>WID_M200D5_1033</t>
-        </is>
-      </c>
+          <t>SKIF_RD1605H</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2017 / WIDIA достижения</t>
+          <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT200-100A32R10RD12-IK</t>
+          <t>MT200-160C40R08RD20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -873,40 +905,40 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RDN..1204MO..N</t>
+          <t>RDN.2006MO..N</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -914,12 +946,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx040</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>SKIF_RD1204H</t>
+          <t>SKIF_RD2006H</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -929,17 +961,17 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>SKIF_RD1204H</t>
+          <t>SKIF_RD2006H</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -949,54 +981,64 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT200-125B40R10RD16</t>
+          <t>R200-038Q22-12M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>SANDVIK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CoroMillⓇ 200 face milling cutter</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>106.4</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>3500</v>
+        <v>18800</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3</v>
+        <v>0.66</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RDN..1605MO..N</t>
+          <t>metric RCKT 1204M0</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1004,12 +1046,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx040</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>COR_RC1204H</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1029,16 +1071,22 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>SKIF_RD1605H</t>
+          <t>SAND_RC1204_H</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
